--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,146 +737,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,146 +870,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
-</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1051,146 +1003,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">079
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
-</t>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1208,146 +1136,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
-</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0150
-</t>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>790</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1365,146 +1269,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1522,68 +1402,57 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
-</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>739</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1599,62 +1468,52 @@
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3805
-</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4145
-</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1672,135 +1531,113 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83499
-</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>274</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 77
-</t>
+          <t>2 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>761</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="Z10" s="3" t="n"/>
@@ -1819,146 +1656,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5093
-</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>268</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1976,146 +1789,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087
-</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>121</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2133,146 +1922,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
-</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">994
-</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2290,146 +2055,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
-</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>183</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">467
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">849
-</t>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2447,146 +2188,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310
-</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">508
-</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>157</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>207</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2605,62 +2322,52 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568 1
-</t>
+          <t>568 8</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
-</t>
+          <t>395</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2670,68 +2377,57 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4898
-</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
-</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6039
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9582
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019
-</t>
+          <t>807</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3640
-</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2754,141 +2450,118 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
-</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3620
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2906,62 +2579,52 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8455
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2969,82 +2632,69 @@
           <t>16</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3062,38 +2712,32 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3103,104 +2747,87 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">072
-</t>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3218,146 +2845,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2140
-</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
-</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>224</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3375,146 +2978,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
-</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">027
-</t>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>127</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
-</t>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3532,146 +3111,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9890
-</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>129</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">087
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3689,146 +3244,122 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23223
-</t>
+          <t>23203</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
-</t>
+          <t>944</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24930
-</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
-</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
-</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3846,134 +3377,112 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4641
-</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3983,8 +3492,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4002,146 +3510,122 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4889
-</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4159,146 +3643,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
-</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 2
-</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4316,146 +3776,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
-</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12130
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4473,146 +3909,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
-</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4630,146 +4042,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5233
-</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4787,86 +4175,72 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2284
-</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5271
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -4876,56 +4250,47 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148
-</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
-</t>
+          <t>554</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
-</t>
+          <t>995</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4943,32 +4308,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520
-</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4978,105 +4338,88 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730 0
-</t>
+          <t>730 2</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
-</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5094,136 +4437,114 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200
-</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2646
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="Y32" s="3" t="n"/>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5241,146 +4562,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
-</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
-</t>
+          <t>799</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5398,146 +4695,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
-</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">078
-</t>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5555,146 +4828,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
-</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5712,146 +4961,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
-</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">033
-</t>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5869,141 +5094,118 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
-</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
-</t>
+          <t>947</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
-</t>
+          <t>460</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="n"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
-</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3593
-</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6021,141 +5223,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6178,135 +5361,113 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t>269 2</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>266</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0
-</t>
+          <t>19 0</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="W39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6324,146 +5485,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3359
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>103</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1695
-</t>
+          <t>695</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>175</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6481,146 +5618,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2894
-</t>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>284</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">049
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6638,122 +5751,102 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
-</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125 7
-</t>
+          <t>15 7</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="S42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="3" t="n"/>
@@ -6775,8 +5868,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -6817,8 +5909,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6859,146 +5950,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19812
-</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
-</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
-</t>
+          <t>756</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
-</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8319
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">673
-</t>
+          <t>673</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630
-</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7016,146 +6083,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">541
-</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
